--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -2961,16 +2961,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -2983,7 +2975,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
+          <t>Boron is not recovered: no process at this scale separates a trace dopant out of a ground board. Written as a definite 0 with NO range, like `rest`, rather than 0 with a band up to 0.1 -- that band said "maybe a tenth of it" on no evidence at all, and it left this group with one ranged row against one fixed one, which src/sampling.py rightly refuses: the constraint pins the loss at 1 - B, so B's range would be discarded without a word.</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
     </row>
@@ -521,11 +521,6 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>material_suffix</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>_mixed</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1126,7 +1121,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2065,12 +2060,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2080,7 +2075,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2127,12 +2122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2142,7 +2137,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2189,12 +2184,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2204,7 +2199,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2251,12 +2246,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2266,7 +2261,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2313,12 +2308,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2328,7 +2323,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2375,12 +2370,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2390,7 +2385,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2437,12 +2432,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2452,7 +2447,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2499,12 +2494,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2514,7 +2509,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2561,12 +2556,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2576,7 +2571,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2623,12 +2618,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2638,7 +2633,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2685,12 +2680,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2700,7 +2695,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2747,12 +2742,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2762,7 +2757,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2809,12 +2804,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2824,7 +2819,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2871,12 +2866,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2886,7 +2881,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2933,12 +2928,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2948,7 +2943,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2987,12 +2982,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3002,7 +2997,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3041,12 +3036,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3056,7 +3051,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3103,12 +3098,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3118,7 +3113,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3165,12 +3160,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3180,7 +3175,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3227,12 +3222,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3242,7 +3237,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3289,12 +3284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3304,7 +3299,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3351,12 +3346,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3366,7 +3361,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3413,12 +3408,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3428,7 +3423,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3475,12 +3470,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3490,7 +3485,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3537,12 +3532,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3552,7 +3547,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3599,12 +3594,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3614,7 +3609,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3661,12 +3656,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3676,7 +3671,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3723,12 +3718,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3738,7 +3733,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3785,12 +3780,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3800,7 +3795,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3847,12 +3842,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3862,7 +3857,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3909,12 +3904,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3924,7 +3919,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3971,12 +3966,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3986,7 +3981,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4033,12 +4028,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4048,7 +4043,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4095,12 +4090,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4110,7 +4105,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4157,12 +4152,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4172,7 +4167,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4219,12 +4214,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4234,7 +4229,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4281,12 +4276,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4296,7 +4291,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4343,12 +4338,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4358,7 +4353,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4405,12 +4400,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4420,7 +4415,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4467,12 +4462,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4482,7 +4477,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4529,12 +4524,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4544,7 +4539,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4591,12 +4586,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4606,7 +4601,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4653,12 +4648,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4668,7 +4663,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4715,12 +4710,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4730,7 +4725,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4777,12 +4772,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4792,7 +4787,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4831,12 +4826,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4846,7 +4841,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,11 +613,6 @@
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_residual</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -684,7 +679,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -694,12 +689,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PCB_mixed</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -710,11 +705,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>material</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -731,7 +721,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F_not_separated</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -741,12 +731,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sensors_mixed</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>F_not_separated</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -757,11 +747,6 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>element</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -773,12 +758,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -790,12 +775,12 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_separated</t>
+          <t>F_recovered_own</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>F_separated</t>
+          <t>F_recovered_own</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -805,6 +790,16 @@
       </c>
     </row>
     <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Dy</t>
@@ -927,15 +922,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1047,7 +1042,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>stays_in_car</t>
+          <t>general_shredder</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1062,7 +1057,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>handoff</t>
         </is>
       </c>
     </row>
@@ -1130,108 +1125,12 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F_alalloy_general</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>general_recycling</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>F_fealloy_general</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>general_recycling</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>F_loss_general</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>general_recycling</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+    <dataValidation sqref="E2:E6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
       <formula1>=_lists!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+    <dataValidation sqref="F2:F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
       <formula1>=_lists!$C$2:$C$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -1245,21 +1144,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1355,10 +1254,8 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="G2" t="n">
+        <v>0.6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1417,10 +1314,8 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1479,13 +1374,9 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>stays_in_car</t>
@@ -1533,10 +1424,8 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="G5" t="n">
+        <v>0.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1595,10 +1484,8 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
+      <c r="G6" t="n">
+        <v>0.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1657,13 +1544,9 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>stays_in_car</t>
@@ -1683,367 +1566,355 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F_alalloy_general</t>
+          <t>F_recovered_own</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a board torn apart in the shredder keeps NO element. Its metal reports to the general aluminium stream as part of the alloy, which is recovered mass but lost gold, silver and palladium.</t>
+          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F_fealloy_general</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a board torn apart in the shredder keeps NO element. Its metal reports to the general steel stream as part of the alloy, which is recovered mass but lost gold, silver and palladium.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F_loss_general</t>
+          <t>F_recovered_own</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.95</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
+          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F_alalloy_general</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a board torn apart in the shredder keeps NO element. Its metal reports to the general aluminium stream as part of the alloy, which is recovered mass but lost gold, silver and palladium.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F_fealloy_general</t>
+          <t>F_recovered_own</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a board torn apart in the shredder keeps NO element. Its metal reports to the general steel stream as part of the alloy, which is recovered mass but lost gold, silver and palladium.</t>
+          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F_loss_general</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>material</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>specialist_recycling</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>shredder</t>
+          <t>grinding_then_element</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2080,24 +1951,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ag</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -2110,7 +1979,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
+          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
         </is>
       </c>
     </row>
@@ -2142,22 +2011,20 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ag</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.15</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2204,13 +2071,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.95</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2266,13 +2131,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2313,7 +2176,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2328,17 +2191,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.95</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2375,7 +2236,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2390,22 +2251,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2437,7 +2296,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2452,22 +2311,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.95</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2482,7 +2339,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
+          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2356,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2514,22 +2371,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2561,7 +2416,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2576,23 +2431,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pd</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2606,7 +2449,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
+          <t>Boron is not recovered: no process at this scale separates a trace dopant out of a ground board. Written as a definite 0 with NO range, like `rest`, rather than 0 with a band up to 0.1 -- that band said "maybe a tenth of it" on no evidence at all, and it left this group with one ranged row against one fixed one, which src/sampling.py rightly refuses: the constraint pins the loss at 1 - B, so B's range would be discarded without a word.</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2466,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2638,23 +2481,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pd</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2700,22 +2531,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ag</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2730,7 +2559,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
+          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
         </is>
       </c>
     </row>
@@ -2762,22 +2591,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ag</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2824,17 +2651,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2886,22 +2711,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2948,16 +2771,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -2970,7 +2799,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Boron is not recovered: no process at this scale separates a trace dopant out of a ground board. Written as a definite 0 with NO range, like `rest`, rather than 0 with a band up to 0.1 -- that band said "maybe a tenth of it" on no evidence at all, and it left this group with one ranged row against one fixed one, which src/sampling.py rightly refuses: the constraint pins the loss at 1 - B, so B's range would be discarded without a word.</t>
+          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
         </is>
       </c>
     </row>
@@ -3002,16 +2831,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -3056,22 +2891,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.02</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3086,7 +2919,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
+          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
         </is>
       </c>
     </row>
@@ -3118,22 +2951,20 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.98</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.984</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3180,22 +3011,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.02</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3210,7 +3039,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
+          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
         </is>
       </c>
     </row>
@@ -3242,22 +3071,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.98</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.984</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3304,13 +3131,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dy</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3366,13 +3191,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dy</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.95</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3428,13 +3251,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ga</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3443,7 +3264,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3490,22 +3311,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ga</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.95</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3552,13 +3371,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ge</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.05</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3567,7 +3384,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3614,22 +3431,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ge</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.95</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3676,13 +3491,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.05</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3738,13 +3551,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.95</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3800,22 +3611,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.85</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3830,7 +3639,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
+          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
         </is>
       </c>
     </row>
@@ -3862,22 +3671,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.15</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3924,22 +3731,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mn</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.95</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3954,7 +3759,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
+          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
         </is>
       </c>
     </row>
@@ -3986,22 +3791,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mn</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.05</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4048,13 +3851,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nd</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4063,7 +3864,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4110,22 +3911,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nd</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.9</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4172,22 +3971,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.02</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4202,7 +3999,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.</t>
+          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
         </is>
       </c>
     </row>
@@ -4234,22 +4031,20 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.98</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.984</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4296,22 +4091,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pt</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.05</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4326,7 +4119,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.</t>
+          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
         </is>
       </c>
     </row>
@@ -4358,22 +4151,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pt</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.95</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4405,12 +4196,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sensors</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>F_recovered_own</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4420,23 +4211,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ta</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4450,7 +4229,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
+          <t>Unspecified material -- board laminate, plastics. Not recovered.</t>
         </is>
       </c>
     </row>
@@ -4482,23 +4261,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ta</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4512,367 +4279,31 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>F_recovered_own</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0.686</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>F_recovered_own</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0.665</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
           <t>Unspecified material -- board laminate, plastics. Not recovered.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>F_disassembled</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Unspecified material -- board laminate, plastics. Not recovered.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="A2:A53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$D$2:$D$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$E$2:$E$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$G$2:$G$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$H$2:$H$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$I$2:$I$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -11,6 +11,7 @@
     <sheet name="_lists" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="processes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TCs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TCs_improved" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -523,6 +524,7 @@
           <t>material_suffix</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -545,6 +547,30 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>200000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>improvement_start</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>improvement_end</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2060</t>
         </is>
       </c>
     </row>
@@ -4306,4 +4332,3258 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Input_FlowID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input_layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input_layer_key</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Output_FlowID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TC_target_layer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TC_target_key</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>value_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>value_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- a main board is a discrete part in a known place, so a worker looking for it finds it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stays_in_car</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>definitional</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: DEFINITIONAL: the car goes to the shredder, so what is in it goes too.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- sensors are scattered through the car in tens of places and most are never sought.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stays_in_car</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>definitional</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: DEFINITIONAL: the car goes to the shredder, so what is in it goes too.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.105</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: Boron is not recovered: no process at this scale separates a trace dopant out of a ground board. Written as a definite 0 with NO range, like `rest`, rather than 0 with a band up to 0.1 -- that band said "maybe a tenth of it" on no evidence at all, and it left this group with one ranged row against one fixed one, which src/sampling.py rightly refuses: the constraint pins the loss at 1 - B, so B's range would be discarded without a word.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.686</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.686</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- collected with the copper rather than by a process of its own.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.105</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- what the specialist route is built around: its own process, and a price that pays for it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.686</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.984</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- no process of its own at this scale; it goes to the slag.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: Unspecified material -- board laminate, plastics. Not recovered.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>specialist_recycling</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>grinding_then_element</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: Unspecified material -- board laminate, plastics. Not recovered.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -524,7 +524,6 @@
           <t>material_suffix</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,18 +1172,18 @@
   <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1280,8 +1279,10 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.6</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1340,8 +1341,10 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0.4</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1400,8 +1403,20 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1450,8 +1465,10 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0.3</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1510,8 +1527,10 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0.7</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1570,8 +1589,20 @@
           <t>Sensors</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1620,8 +1651,10 @@
           <t>Ag</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0.95</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1680,8 +1713,10 @@
           <t>Ag</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0.05</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1740,8 +1775,10 @@
           <t>Au</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0.95</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1800,8 +1837,10 @@
           <t>Au</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0.05</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1860,8 +1899,10 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0.9</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1920,8 +1961,10 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1980,8 +2023,10 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0.85</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2040,8 +2085,10 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0.15</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2100,8 +2147,10 @@
           <t>Pd</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.95</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2160,8 +2209,10 @@
           <t>Pd</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0.05</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2220,8 +2271,10 @@
           <t>Ag</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0.95</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2280,8 +2333,10 @@
           <t>Ag</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0.05</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2340,8 +2395,10 @@
           <t>Au</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0.95</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2400,8 +2457,10 @@
           <t>Au</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0.05</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2460,8 +2519,20 @@
           <t>B</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2510,8 +2581,20 @@
           <t>B</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2560,8 +2643,10 @@
           <t>Co</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0.6</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2620,8 +2705,10 @@
           <t>Co</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0.4</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2680,8 +2767,10 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0.9</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2740,8 +2829,10 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0.1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2800,8 +2891,10 @@
           <t>Dy</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0.05</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2860,8 +2953,10 @@
           <t>Dy</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0.95</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2920,8 +3015,10 @@
           <t>Ga</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0.02</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2980,8 +3077,10 @@
           <t>Ga</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0.98</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3040,8 +3139,10 @@
           <t>Ge</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0.02</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3100,8 +3201,10 @@
           <t>Ge</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0.98</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3160,8 +3263,10 @@
           <t>In</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0.05</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3220,8 +3325,10 @@
           <t>In</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0.95</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3280,8 +3387,10 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0.05</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3340,8 +3449,10 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0.95</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3400,8 +3511,10 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0.05</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3460,8 +3573,10 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0.95</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3520,8 +3635,10 @@
           <t>Nd</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0.05</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3580,8 +3697,10 @@
           <t>Nd</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0.95</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3640,8 +3759,10 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0.85</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3700,8 +3821,10 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0.15</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3760,8 +3883,10 @@
           <t>Pt</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0.95</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3820,8 +3945,10 @@
           <t>Pt</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0.05</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3880,8 +4007,10 @@
           <t>Ta</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0.1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3940,8 +4069,10 @@
           <t>Ta</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0.9</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4000,8 +4131,10 @@
           <t>Ti</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0.02</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4060,8 +4193,10 @@
           <t>Ti</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0.98</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4120,8 +4255,10 @@
           <t>W</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0.05</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4180,8 +4317,10 @@
           <t>W</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0.95</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4240,8 +4379,20 @@
           <t>rest</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>1</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4290,8 +4441,20 @@
           <t>rest</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>1</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4310,26 +4473,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="A2:A53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$D$2:$D$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$E$2:$E$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$G$2:$G$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$H$2:$H$22</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$I$2:$I$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4579,6 +4722,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>stays_in_car</t>
@@ -4755,6 +4908,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>stays_in_car</t>
@@ -5675,6 +5838,16 @@
           <t>0</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -5727,6 +5900,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -7515,6 +7698,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>specialist_recycling</t>
@@ -7563,6 +7756,16 @@
         </is>
       </c>
       <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_lists" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="_lists" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="processes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TCs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="TCs_improved" sheetId="5" state="visible" r:id="rId5"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,22 +29,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,9 +50,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,18 +419,14 @@
   </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -524,6 +510,7 @@
           <t>material_suffix</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -574,11 +561,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$A$2:$A$3</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -734,6 +716,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>element</t>
@@ -776,6 +759,8 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>intermediate</t>
@@ -786,6 +771,8 @@
           <t>F_loss_own</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>F_loss_own</t>
@@ -796,13 +783,19 @@
           <t>Co</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>F_recovered_own</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>F_recovered_own</t>
@@ -813,13 +806,19 @@
           <t>Cu</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>F_shredded</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>F_shredded</t>
@@ -830,111 +829,232 @@
           <t>Dy</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Ga</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Li</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Mn</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Ni</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Pd</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Pt</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Sensors</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Ta</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Ti</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>rest</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -947,44 +1067,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>keyed_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -1067,7 +1179,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>general_shredder</t>
+          <t>stays_in_car</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1082,7 +1194,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>handoff</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -1094,71 +1206,159 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F_recovered_own</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>grinding</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>mill</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>F_recovered_own</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>element_recovery</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>one_per_element</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>F_loss_own</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>element_recovery</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>one_per_element</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="E2:E6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$B$2:$B$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$C$2:$C$5</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1169,80 +1369,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Input_layer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Input_layer_key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>TC_target_key</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>value_min</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>value_max</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -1623,7 +1809,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1668,12 +1854,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1685,7 +1871,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1730,12 +1916,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1747,7 +1933,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1792,12 +1978,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1809,7 +1995,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1854,12 +2040,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1871,7 +2057,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1916,12 +2102,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1933,7 +2119,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1978,12 +2164,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1995,7 +2181,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2040,12 +2226,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2057,7 +2243,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2102,12 +2288,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2119,7 +2305,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2164,12 +2350,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2181,7 +2367,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2226,12 +2412,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2243,7 +2429,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2288,12 +2474,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2305,7 +2491,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,12 +2536,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2367,7 +2553,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2412,12 +2598,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2429,7 +2615,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2474,12 +2660,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2491,7 +2677,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2536,12 +2722,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2553,7 +2739,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2598,12 +2784,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2615,7 +2801,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2660,12 +2846,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2677,7 +2863,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2722,12 +2908,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2739,7 +2925,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2784,12 +2970,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2801,7 +2987,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2846,12 +3032,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2863,7 +3049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2908,12 +3094,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2925,7 +3111,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2970,12 +3156,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2987,7 +3173,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3032,12 +3218,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3049,7 +3235,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3094,12 +3280,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3111,7 +3297,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,12 +3342,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3173,7 +3359,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3218,12 +3404,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3235,7 +3421,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3280,12 +3466,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3297,7 +3483,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3342,12 +3528,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3359,7 +3545,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3404,12 +3590,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3421,7 +3607,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3466,12 +3652,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3483,7 +3669,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3528,12 +3714,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3545,7 +3731,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3590,12 +3776,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3607,7 +3793,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3652,12 +3838,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3669,7 +3855,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3714,12 +3900,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3731,7 +3917,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3776,12 +3962,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3793,7 +3979,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,12 +4024,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3855,7 +4041,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3900,12 +4086,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3917,7 +4103,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3962,12 +4148,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3979,7 +4165,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4024,12 +4210,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4041,7 +4227,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4086,12 +4272,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4103,7 +4289,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4148,12 +4334,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4165,7 +4351,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4210,12 +4396,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4227,7 +4413,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4272,12 +4458,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4289,7 +4475,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4334,12 +4520,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4351,7 +4537,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4396,12 +4582,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4413,62 +4599,2666 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>element_recovery</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>one_per_element</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Unspecified material -- board laminate, plastics. Not recovered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>F_disassembled</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>grinding</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>mill</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: everything taken out whole is ground, so all of it arrives at the mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Sensors</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>grinding</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>mill</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: everything taken out whole is ground, so all of it arrives at the mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- copper is the one metal a car shredder returns from a board: it survives crushing as sortable pieces and the ferrous and non-ferrous separators find it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus the copper that came back, given its own range. Replace it with a number measured on this side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>rest</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Unspecified material -- board laminate, plastics. Not recovered.</t>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- copper is the one metal a car shredder returns from a board: it survives crushing as sortable pieces and the ferrous and non-ferrous separators find it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus the copper that came back, given its own range. Replace it with a number measured on this side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
         </is>
       </c>
     </row>
@@ -4483,80 +7273,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Input_FlowID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Input_layer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Input_layer_key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Output_FlowID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>TC_target_key</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>value_min</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>value_max</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -4937,7 +7713,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4982,12 +7758,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -4999,7 +7775,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5044,12 +7820,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -5061,7 +7837,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5106,12 +7882,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -5123,7 +7899,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5168,12 +7944,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -5185,7 +7961,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5230,12 +8006,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5247,7 +8023,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5292,12 +8068,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5309,7 +8085,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5354,12 +8130,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -5371,7 +8147,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5416,12 +8192,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -5433,7 +8209,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5478,12 +8254,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -5495,7 +8271,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5540,12 +8316,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5557,7 +8333,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5602,12 +8378,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5619,7 +8395,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5664,12 +8440,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5681,7 +8457,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5726,12 +8502,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5743,7 +8519,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5788,12 +8564,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -5805,7 +8581,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5850,12 +8626,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -5867,7 +8643,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5912,12 +8688,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -5929,7 +8705,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5974,12 +8750,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -5991,7 +8767,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6036,12 +8812,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -6053,7 +8829,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6098,12 +8874,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -6115,7 +8891,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6160,12 +8936,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -6177,7 +8953,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6222,12 +8998,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -6239,7 +9015,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6284,12 +9060,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -6301,7 +9077,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6346,12 +9122,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -6363,7 +9139,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6408,12 +9184,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -6425,7 +9201,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6470,12 +9246,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -6487,7 +9263,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6532,12 +9308,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -6549,7 +9325,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6594,12 +9370,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -6611,7 +9387,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6656,12 +9432,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -6673,7 +9449,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6718,12 +9494,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -6735,7 +9511,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6780,12 +9556,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -6797,7 +9573,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6842,12 +9618,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -6859,7 +9635,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6904,12 +9680,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -6921,7 +9697,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6966,12 +9742,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -6983,7 +9759,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7028,12 +9804,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -7045,7 +9821,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7090,12 +9866,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -7107,7 +9883,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7152,12 +9928,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -7169,7 +9945,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7214,12 +9990,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -7231,7 +10007,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7276,12 +10052,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -7293,7 +10069,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7338,12 +10114,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -7355,7 +10131,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7400,12 +10176,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7417,7 +10193,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7462,12 +10238,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7479,7 +10255,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7524,12 +10300,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -7541,7 +10317,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7586,12 +10362,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -7603,7 +10379,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7648,12 +10424,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7665,7 +10441,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F_disassembled</t>
+          <t>F_ground</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7710,12 +10486,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>specialist_recycling</t>
+          <t>element_recovery</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>grinding_then_element</t>
+          <t>one_per_element</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -7727,62 +10503,2666 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>element_recovery</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>one_per_element</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: Unspecified material -- board laminate, plastics. Not recovered.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>F_disassembled</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>grinding</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>mill</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: everything taken out whole is ground, so all of it arrives at the mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F_disassembled</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F_ground</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Sensors</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>F_loss_own</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>grinding</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>mill</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: everything taken out whole is ground, so all of it arrives at the mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- copper is the one metal a car shredder returns from a board: it survives crushing as sortable pieces and the ferrous and non-ferrous separators find it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus the copper that came back, given its own range. Replace it with a number measured on this side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>rest</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>specialist_recycling</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>grinding_then_element</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>SEEDED COPY of the current value -- NOT an improvement. Replace with the number this process reaches once improved, and its range. Until you do, this case ramps from a value to itself and every year is identical. (was: Unspecified material -- board laminate, plastics. Not recovered.)</t>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ag</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- copper is the one metal a car shredder returns from a board: it survives crushing as sortable pieces and the ferrous and non-ferrous separators find it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus the copper that came back, given its own range. Replace it with a number measured on this side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Dy</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ge</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Pd</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Pt</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ta</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>F_shredded</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
         </is>
       </c>
     </row>

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rm/Documents/GitHub/RAWCLICRecoveryModel/data_folder/bev_electronics_boards/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E0C2B7-C2A2-7242-A170-28879A60C4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BBDB31-7D96-BF4A-82AC-F5199743E28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="40580" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="88">
   <si>
     <t>key</t>
   </si>
@@ -280,12 +280,6 @@
   </si>
   <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>DEFINITIONAL: the car goes to the shredder, so what is in it goes too.</t>
@@ -1442,7 +1436,7 @@
         <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1970,7 +1964,7 @@
         <v>73</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -2664,7 +2658,7 @@
         <v>0.6</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s">
         <v>72</v>
@@ -2699,7 +2693,7 @@
         <v>0.1</v>
       </c>
       <c r="I43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s">
         <v>72</v>
@@ -3023,7 +3017,7 @@
         <v>73</v>
       </c>
       <c r="L52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -3061,7 +3055,7 @@
         <v>73</v>
       </c>
       <c r="L53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -3099,7 +3093,7 @@
         <v>71</v>
       </c>
       <c r="L54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -3137,7 +3131,7 @@
         <v>71</v>
       </c>
       <c r="L55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -3175,7 +3169,7 @@
         <v>76</v>
       </c>
       <c r="L56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -3213,7 +3207,7 @@
         <v>76</v>
       </c>
       <c r="L57" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -3251,7 +3245,7 @@
         <v>76</v>
       </c>
       <c r="L58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -3289,7 +3283,7 @@
         <v>76</v>
       </c>
       <c r="L59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -3397,7 +3391,7 @@
         <v>76</v>
       </c>
       <c r="L62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -3435,7 +3429,7 @@
         <v>76</v>
       </c>
       <c r="L63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -3473,7 +3467,7 @@
         <v>76</v>
       </c>
       <c r="L64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -3511,7 +3505,7 @@
         <v>76</v>
       </c>
       <c r="L65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -3549,7 +3543,7 @@
         <v>76</v>
       </c>
       <c r="L66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -3587,7 +3581,7 @@
         <v>76</v>
       </c>
       <c r="L67" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -3625,7 +3619,7 @@
         <v>76</v>
       </c>
       <c r="L68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -3663,7 +3657,7 @@
         <v>76</v>
       </c>
       <c r="L69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -3701,7 +3695,7 @@
         <v>76</v>
       </c>
       <c r="L70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -3739,7 +3733,7 @@
         <v>76</v>
       </c>
       <c r="L71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -3777,7 +3771,7 @@
         <v>76</v>
       </c>
       <c r="L72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -3815,7 +3809,7 @@
         <v>76</v>
       </c>
       <c r="L73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -3853,7 +3847,7 @@
         <v>76</v>
       </c>
       <c r="L74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -3891,7 +3885,7 @@
         <v>76</v>
       </c>
       <c r="L75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -3929,7 +3923,7 @@
         <v>76</v>
       </c>
       <c r="L76" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -3967,7 +3961,7 @@
         <v>76</v>
       </c>
       <c r="L77" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -4005,7 +3999,7 @@
         <v>76</v>
       </c>
       <c r="L78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -4043,7 +4037,7 @@
         <v>76</v>
       </c>
       <c r="L79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -4151,7 +4145,7 @@
         <v>76</v>
       </c>
       <c r="L82" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -4189,7 +4183,7 @@
         <v>76</v>
       </c>
       <c r="L83" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -4227,7 +4221,7 @@
         <v>76</v>
       </c>
       <c r="L84" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -4265,7 +4259,7 @@
         <v>76</v>
       </c>
       <c r="L85" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -4303,7 +4297,7 @@
         <v>76</v>
       </c>
       <c r="L86" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -4341,7 +4335,7 @@
         <v>76</v>
       </c>
       <c r="L87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -4379,7 +4373,7 @@
         <v>76</v>
       </c>
       <c r="L88" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -4417,7 +4411,7 @@
         <v>76</v>
       </c>
       <c r="L89" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -4455,7 +4449,7 @@
         <v>76</v>
       </c>
       <c r="L90" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -4493,7 +4487,7 @@
         <v>76</v>
       </c>
       <c r="L91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -4531,7 +4525,7 @@
         <v>76</v>
       </c>
       <c r="L92" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -4569,7 +4563,7 @@
         <v>76</v>
       </c>
       <c r="L93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -4607,7 +4601,7 @@
         <v>76</v>
       </c>
       <c r="L94" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
@@ -4645,7 +4639,7 @@
         <v>76</v>
       </c>
       <c r="L95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4917,7 +4911,7 @@
         <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -4940,13 +4934,13 @@
         <v>34</v>
       </c>
       <c r="G8">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H8">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="I8">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J8" t="s">
         <v>72</v>
@@ -4975,13 +4969,13 @@
         <v>34</v>
       </c>
       <c r="G9">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H9">
-        <v>3.5000000000000003E-2</v>
+        <v>0.01</v>
       </c>
       <c r="I9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="s">
         <v>72</v>
@@ -5010,13 +5004,13 @@
         <v>38</v>
       </c>
       <c r="G10">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H10">
-        <v>0.9</v>
+        <v>0.995</v>
       </c>
       <c r="I10">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="s">
         <v>72</v>
@@ -5045,13 +5039,13 @@
         <v>38</v>
       </c>
       <c r="G11">
+        <v>0.02</v>
+      </c>
+      <c r="H11">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I11">
         <v>0.05</v>
-      </c>
-      <c r="H11">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="I11">
-        <v>0.2</v>
       </c>
       <c r="J11" t="s">
         <v>72</v>
@@ -5080,13 +5074,13 @@
         <v>47</v>
       </c>
       <c r="G12">
-        <v>0.94</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H12">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="I12">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="J12" t="s">
         <v>72</v>
@@ -5121,7 +5115,7 @@
         <v>0.02</v>
       </c>
       <c r="I13">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J13" t="s">
         <v>72</v>
@@ -5150,13 +5144,13 @@
         <v>56</v>
       </c>
       <c r="G14">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="H14">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I14">
-        <v>0.85</v>
+        <v>0.94</v>
       </c>
       <c r="J14" t="s">
         <v>72</v>
@@ -5185,13 +5179,13 @@
         <v>56</v>
       </c>
       <c r="G15">
+        <v>0.12</v>
+      </c>
+      <c r="H15">
+        <v>0.05</v>
+      </c>
+      <c r="I15">
         <v>0.25</v>
-      </c>
-      <c r="H15">
-        <v>0.1</v>
-      </c>
-      <c r="I15">
-        <v>0.35</v>
       </c>
       <c r="J15" t="s">
         <v>72</v>
@@ -5220,13 +5214,13 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>0.92</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="H16">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="I16">
-        <v>0.96</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="J16" t="s">
         <v>72</v>
@@ -5255,13 +5249,13 @@
         <v>57</v>
       </c>
       <c r="G17">
-        <v>0.08</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="H17">
         <v>0.02</v>
       </c>
       <c r="I17">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="s">
         <v>72</v>
@@ -5290,13 +5284,13 @@
         <v>34</v>
       </c>
       <c r="G18">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H18">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="I18">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J18" t="s">
         <v>72</v>
@@ -5325,13 +5319,13 @@
         <v>34</v>
       </c>
       <c r="G19">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H19">
-        <v>3.5000000000000003E-2</v>
+        <v>0.01</v>
       </c>
       <c r="I19">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="s">
         <v>72</v>
@@ -5360,13 +5354,13 @@
         <v>38</v>
       </c>
       <c r="G20">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H20">
-        <v>0.9</v>
+        <v>0.995</v>
       </c>
       <c r="I20">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="J20" t="s">
         <v>72</v>
@@ -5395,13 +5389,13 @@
         <v>38</v>
       </c>
       <c r="G21">
+        <v>0.02</v>
+      </c>
+      <c r="H21">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I21">
         <v>0.05</v>
-      </c>
-      <c r="H21">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="I21">
-        <v>0.2</v>
       </c>
       <c r="J21" t="s">
         <v>72</v>
@@ -5430,13 +5424,13 @@
         <v>42</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="J22" t="s">
         <v>72</v>
@@ -5445,7 +5439,7 @@
         <v>73</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -5468,10 +5462,10 @@
         <v>42</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H23">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -5503,13 +5497,13 @@
         <v>45</v>
       </c>
       <c r="G24">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="H24">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I24">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="s">
         <v>72</v>
@@ -5538,13 +5532,13 @@
         <v>45</v>
       </c>
       <c r="G25">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="H25">
-        <v>0.55000000000000004</v>
+        <v>0.1</v>
       </c>
       <c r="I25">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="s">
         <v>72</v>
@@ -5573,13 +5567,13 @@
         <v>47</v>
       </c>
       <c r="G26">
-        <v>0.94</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H26">
-        <v>0.88</v>
-      </c>
-      <c r="I26" t="s">
-        <v>82</v>
+        <v>0.95</v>
+      </c>
+      <c r="I26">
+        <v>0.99</v>
       </c>
       <c r="J26" t="s">
         <v>72</v>
@@ -5613,8 +5607,8 @@
       <c r="H27">
         <v>0.02</v>
       </c>
-      <c r="I27" t="s">
-        <v>81</v>
+      <c r="I27">
+        <v>0.15</v>
       </c>
       <c r="J27" t="s">
         <v>72</v>
@@ -5643,13 +5637,13 @@
         <v>49</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I28">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="J28" t="s">
         <v>72</v>
@@ -5678,13 +5672,13 @@
         <v>49</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H29">
+        <v>0.25</v>
+      </c>
+      <c r="I29">
         <v>0.75</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
       </c>
       <c r="J29" t="s">
         <v>72</v>
@@ -5713,13 +5707,13 @@
         <v>50</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I30">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="s">
         <v>72</v>
@@ -5748,13 +5742,13 @@
         <v>50</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H31">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="s">
         <v>72</v>
@@ -5783,13 +5777,13 @@
         <v>51</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I32">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="J32" t="s">
         <v>72</v>
@@ -5818,13 +5812,13 @@
         <v>51</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H33">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="s">
         <v>72</v>
@@ -5853,13 +5847,13 @@
         <v>52</v>
       </c>
       <c r="G34">
-        <v>0.05</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I34">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="J34" t="s">
         <v>72</v>
@@ -5888,13 +5882,13 @@
         <v>52</v>
       </c>
       <c r="G35">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H35">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="I35">
-        <v>0.98</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="s">
         <v>72</v>
@@ -5923,13 +5917,13 @@
         <v>53</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0.02</v>
+        <v>0.35</v>
       </c>
       <c r="J36" t="s">
         <v>72</v>
@@ -5958,13 +5952,13 @@
         <v>53</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H37">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J37" t="s">
         <v>72</v>
@@ -5993,13 +5987,13 @@
         <v>54</v>
       </c>
       <c r="G38">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I38">
-        <v>0.15</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J38" t="s">
         <v>72</v>
@@ -6028,13 +6022,13 @@
         <v>54</v>
       </c>
       <c r="G39">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="H39">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="s">
         <v>72</v>
@@ -6063,13 +6057,13 @@
         <v>55</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I40">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="s">
         <v>72</v>
@@ -6098,13 +6092,13 @@
         <v>55</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H41">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="s">
         <v>72</v>
@@ -6133,13 +6127,13 @@
         <v>56</v>
       </c>
       <c r="G42">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="H42">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I42">
-        <v>0.98</v>
+        <v>0.94</v>
       </c>
       <c r="J42" t="s">
         <v>72</v>
@@ -6168,10 +6162,10 @@
         <v>56</v>
       </c>
       <c r="G43">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H43">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I43">
         <v>0.25</v>
@@ -6203,13 +6197,13 @@
         <v>58</v>
       </c>
       <c r="G44">
-        <v>0.88</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="H44">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I44">
-        <v>0.93</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" t="s">
         <v>72</v>
@@ -6238,13 +6232,13 @@
         <v>58</v>
       </c>
       <c r="G45">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H45">
+        <v>0.02</v>
+      </c>
+      <c r="I45">
         <v>0.12</v>
-      </c>
-      <c r="H45">
-        <v>0.05</v>
-      </c>
-      <c r="I45">
-        <v>0.25</v>
       </c>
       <c r="J45" t="s">
         <v>72</v>
@@ -6273,13 +6267,13 @@
         <v>59</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I46">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="J46" t="s">
         <v>72</v>
@@ -6308,13 +6302,13 @@
         <v>59</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H47">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="s">
         <v>72</v>
@@ -6343,13 +6337,13 @@
         <v>60</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I48">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="J48" t="s">
         <v>72</v>
@@ -6378,13 +6372,13 @@
         <v>60</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H49">
+        <v>0.6</v>
+      </c>
+      <c r="I49">
         <v>0.9</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
       </c>
       <c r="J49" t="s">
         <v>72</v>
@@ -6413,13 +6407,13 @@
         <v>61</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I50">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="s">
         <v>72</v>
@@ -6448,13 +6442,13 @@
         <v>61</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H51">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="s">
         <v>72</v>
@@ -6498,7 +6492,7 @@
         <v>73</v>
       </c>
       <c r="L52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -6536,7 +6530,7 @@
         <v>73</v>
       </c>
       <c r="L53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -6574,7 +6568,7 @@
         <v>71</v>
       </c>
       <c r="L54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -6612,7 +6606,7 @@
         <v>71</v>
       </c>
       <c r="L55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -6650,7 +6644,7 @@
         <v>76</v>
       </c>
       <c r="L56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -6688,7 +6682,7 @@
         <v>76</v>
       </c>
       <c r="L57" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -6726,7 +6720,7 @@
         <v>76</v>
       </c>
       <c r="L58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -6764,7 +6758,7 @@
         <v>76</v>
       </c>
       <c r="L59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -6787,13 +6781,13 @@
         <v>47</v>
       </c>
       <c r="G60">
-        <v>0.6</v>
+        <v>0.94</v>
       </c>
       <c r="H60">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="I60">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="J60" t="s">
         <v>75</v>
@@ -6822,13 +6816,13 @@
         <v>47</v>
       </c>
       <c r="G61">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="H61">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="I61">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="J61" t="s">
         <v>75</v>
@@ -6872,7 +6866,7 @@
         <v>76</v>
       </c>
       <c r="L62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -6910,7 +6904,7 @@
         <v>76</v>
       </c>
       <c r="L63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -6948,7 +6942,7 @@
         <v>76</v>
       </c>
       <c r="L64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -6986,7 +6980,7 @@
         <v>76</v>
       </c>
       <c r="L65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -7024,7 +7018,7 @@
         <v>76</v>
       </c>
       <c r="L66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -7062,7 +7056,7 @@
         <v>76</v>
       </c>
       <c r="L67" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -7100,7 +7094,7 @@
         <v>76</v>
       </c>
       <c r="L68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -7138,7 +7132,7 @@
         <v>76</v>
       </c>
       <c r="L69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -7176,7 +7170,7 @@
         <v>76</v>
       </c>
       <c r="L70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -7214,7 +7208,7 @@
         <v>76</v>
       </c>
       <c r="L71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -7252,7 +7246,7 @@
         <v>76</v>
       </c>
       <c r="L72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -7290,7 +7284,7 @@
         <v>76</v>
       </c>
       <c r="L73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -7328,7 +7322,7 @@
         <v>76</v>
       </c>
       <c r="L74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -7366,7 +7360,7 @@
         <v>76</v>
       </c>
       <c r="L75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -7404,7 +7398,7 @@
         <v>76</v>
       </c>
       <c r="L76" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -7442,7 +7436,7 @@
         <v>76</v>
       </c>
       <c r="L77" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -7480,7 +7474,7 @@
         <v>76</v>
       </c>
       <c r="L78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -7518,7 +7512,7 @@
         <v>76</v>
       </c>
       <c r="L79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -7541,13 +7535,13 @@
         <v>47</v>
       </c>
       <c r="G80">
-        <v>0.6</v>
+        <v>0.94</v>
       </c>
       <c r="H80">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="I80">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="J80" t="s">
         <v>75</v>
@@ -7576,13 +7570,13 @@
         <v>47</v>
       </c>
       <c r="G81">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="H81">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="I81">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="J81" t="s">
         <v>75</v>
@@ -7626,7 +7620,7 @@
         <v>76</v>
       </c>
       <c r="L82" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -7664,7 +7658,7 @@
         <v>76</v>
       </c>
       <c r="L83" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -7702,7 +7696,7 @@
         <v>76</v>
       </c>
       <c r="L84" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -7740,7 +7734,7 @@
         <v>76</v>
       </c>
       <c r="L85" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -7778,7 +7772,7 @@
         <v>76</v>
       </c>
       <c r="L86" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -7816,7 +7810,7 @@
         <v>76</v>
       </c>
       <c r="L87" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -7854,7 +7848,7 @@
         <v>76</v>
       </c>
       <c r="L88" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -7892,7 +7886,7 @@
         <v>76</v>
       </c>
       <c r="L89" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -7930,7 +7924,7 @@
         <v>76</v>
       </c>
       <c r="L90" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -7968,7 +7962,7 @@
         <v>76</v>
       </c>
       <c r="L91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -8006,7 +8000,7 @@
         <v>76</v>
       </c>
       <c r="L92" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -8044,7 +8038,7 @@
         <v>76</v>
       </c>
       <c r="L93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -8082,7 +8076,7 @@
         <v>76</v>
       </c>
       <c r="L94" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
@@ -8120,7 +8114,7 @@
         <v>76</v>
       </c>
       <c r="L95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rm/Documents/GitHub/RAWCLICRecoveryModel/data_folder/bev_electronics_boards/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BBDB31-7D96-BF4A-82AC-F5199743E28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BDBD36-A667-A945-9A3E-B06C616055B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="40580" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5007,10 +5007,10 @@
         <v>0.98</v>
       </c>
       <c r="H10">
+        <v>0.96</v>
+      </c>
+      <c r="I10">
         <v>0.995</v>
-      </c>
-      <c r="I10">
-        <v>0.96</v>
       </c>
       <c r="J10" t="s">
         <v>72</v>
@@ -5357,10 +5357,10 @@
         <v>0.98</v>
       </c>
       <c r="H20">
+        <v>0.96</v>
+      </c>
+      <c r="I20">
         <v>0.995</v>
-      </c>
-      <c r="I20">
-        <v>0.96</v>
       </c>
       <c r="J20" t="s">
         <v>72</v>

--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rm/Documents/GitHub/RAWCLICRecoveryModel/data_folder/bev_electronics_boards/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BDBD36-A667-A945-9A3E-B06C616055B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F1F42F-4E81-B44B-B379-F785C5A575E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="40580" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43200" yWindow="600" windowWidth="40580" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="1" r:id="rId1"/>
@@ -5109,13 +5109,13 @@
         <v>47</v>
       </c>
       <c r="G13">
-        <v>0.06</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H13">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I13">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="J13" t="s">
         <v>72</v>
@@ -5602,13 +5602,13 @@
         <v>47</v>
       </c>
       <c r="G27">
-        <v>0.06</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H27">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I27">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="J27" t="s">
         <v>72</v>
